--- a/docs/triton-learning/cards/triton-lesson-05-layer-norm-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-05-layer-norm-technical-qa.xlsx
@@ -36,15 +36,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">末维 LayerNorm 怎样映射成 M×N？</t>
+          <t xml:space="preserve">对形状为 \[d₀,…,dₖ,N\] 的 tensor 只沿最后一维做 LayerNorm 时，怎样把计算看成 \[M,N\]，并确定行统计量与仿射参数 w、b 的形状？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：把所有前导维展平为 M 行，把被归一化的最后一维作为 N 列。
-• [T#B#统计量]：每行一份 mean/rstd，紧凑存储为 \[M\]；广播观察可写成 \[M,1\]。
-• [T#B#参数]：所有行共享 w/b，紧凑存储为 \[N\]；广播观察可写成 \[1,N\]。
-[T#B,!c47f17#边界]：参数共享不会让一行输入参与另一行的前向统计量。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：把所有前导维的组合视为 M 行，每行有 N 个待共同归一化的特征；统计量按行独立保存，仿射参数按特征列在所有行之间共享。
+• [T#B#行列映射]：M=d₀×…×dₖ，N 是最后一维长度。例如输入 \[B,T,N\] 可看成 \[B×T,N\]：每个 batch/token 对应一行。
+• [T#B#行统计量]：每行计算一个均值 mean 和一个标准差倒数 rstd=1/sqrt(variance+epsilon)，其中 epsilon 是稳定分母的正数。紧凑保存时二者各为 \[M\]；参与逐元素计算时，可按 \[M,1\] 沿列广播。
+• [T#B#仿射参数]：归一化后执行 y=x_hat×w+b。w 是缩放参数、b 是偏置参数，各为 \[N\]；它们可按 \[1,N\] 沿行广播，所有行使用同一列对应的参数。
+[T#B,!c47f17#边界]：参数跨行共享，不意味着前向统计量跨行计算。保持 w、b 不变时，修改一行输入不会改变其他行的均值、方差或前向输出。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -61,15 +62,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padding load 为0，方差为何仍可能出错？</t>
+          <t xml:space="preserve">逐行 LayerNorm 用一个比行长 N 更大的计算块处理尾部。即使 load 时给无效位置补了 0，为什么计算方差前仍需在减均值后再次把无效位置置零？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：因为减去行均值后，无效 lane 会从0变成 -mean，并把 mean² 错加进方差。
-• [T#B#正确不变量]：中心化完成后，用 mask 把无效 lane 在 FP32 中明确归零，再平方归约。
-• [T#B#精度边界]：FP16 load 的 other=mean 可能先量化 mean；转回 FP32 也可能留下 padding 残差。
-[T#B,!c47f17#边界]：mask 不只保护访存，还要保护归约域的数学语义。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为填入的 0 在减去行均值后会变成 −mean；若继续平方并求和，无效位置就会额外贡献 mean²，污染本应只包含 N 个有效元素的方差。
+• [T#B#具体误差]：例如 N=5、计算块含 8 个位置、行均值为 2。三个无效位置若都参与平方，会多加 3×(−2)²=12，再除以 N=5，使方差额外增加 2.4。
+• [T#B#正确处理]：先以 FP32 计算有效元素的中心化值 x−mean，再把无效位置明确置为 0，最后平方、求和并除以有效长度 N。关键是不让 padding 对方差分子有任何贡献。
+• [T#B#为何不能只补 mean]：若 FP16 load 使用 other=mean，FP32 的 mean 可能先被舍入为 FP16；随后转回 FP32 并减原始 mean，padding 仍可能留下非零残差。
+[T#B,!c47f17#边界]：load mask 保证地址合法，并不自动保证后续变换的数学中性。方差归约中需要的是中心化后的无效贡献严格为零。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -86,15 +88,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LayerNorm 的 dw、db 沿哪个维度归约？</t>
+          <t xml:space="preserve">输入 X 为 \[M,N\]、每行独立归一化，前向为 Yᵢⱼ=x_hatᵢⱼ×wⱼ+bⱼ，其中 w、b 在所有行间共享。已知上游梯度 dY，参数梯度 dw、db 应如何计算、沿哪个轴归约？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它们对共享参数的同一特征列跨 M 行求和。
-[E##dw_j=\sum_i dy_{ij}\hat{x}_{ij},\qquad db_j=\sum_i dy_{ij}]
-• [T#B#局部贡献]：每个逐行 program 先产生长度 N 的贡献向量。
-[T#B,!c47f17#边界]：dw 乘的是归一化输入 x_hat，不是原始 x；各行贡献带符号相加，可能抵消。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：对每个特征列 j，把所有 M 行对同一个共享参数的梯度贡献相加；最终 dw、db 的形状都为 \[N\]。
+• [T#B#符号定义]：dYᵢⱼ 是损失对输出 Yᵢⱼ 的梯度；x_hatᵢⱼ 是该行经过减均值、乘 rstd 后的归一化输入。i 遍历行，j 遍历特征列。
+[E##dw_j=\sum_{i=0}^{M-1}dY_{ij}\hat{x}_{ij},\qquad db_j=\sum_{i=0}^{M-1}dY_{ij}]
+• [T#B#局部与全局]：一个逐行 program 只能产生该行的长度 N 贡献向量；它不是最终参数梯度。需要继续沿行维求和，才能把所有使用同一 wⱼ、bⱼ 的贡献合并。
+[T#B,!c47f17#边界]：dw 乘的是归一化输入 x_hat，而不是原始 X；各行贡献带符号相加，可以互相抵消，例如 3 与 −5 的总和是 −2。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -111,15 +114,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">共享 \[G,N\] 槽怎样得到最终 dw/db？</t>
+          <t xml:space="preserve">在 LayerNorm 反向中，M 个逐行 program 要合并共享参数 w、b 的梯度。若 dw、db 分别使用 FP32 的 \[G,N\] 临时槽，怎样从这些槽得到最终 \[N\] 梯度？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：行 program 按 pid mod G 进入组内临界区累加，第二个 kernel 再沿 G 归约。
-• [T#B#临时空间]：dw、db 各有 FP32 \[G,N\] 部分和；同组 program 共用一把锁。
-• [T#B#完整性]：初始化、组映射和第二阶段必须让每行贡献恰好计入一次。
-[T#B,!c47f17#边界]：令 G=M 只把每行分开放置，并不会形成最终 \[N\] 梯度，因此仍需归约。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先把逐行贡献按 program 编号映射到 G 个组，在组锁保护下累加为组部分和；再启动第二个 kernel，沿 G 维归约这些部分和。
+• [T#B#各维含义]：M 是输入行数，N 是共享参数长度，G 是临时槽的组数。每个槽是一条长度 N 的向量，表示分配到该组的若干行的参数梯度贡献之和。
+• [T#B#第一阶段]：第 pid 行使用组号 pid%G。多个 program 若映射到同一组，就必须先获得该组的锁，再读取、更新并写回该组的 dw/db 槽，避免并发覆盖。
+• [T#B#第二阶段]：第一阶段结束后，对每个特征列 j，把组 0 到 G−1 的部分和相加，分别得到最终 dwⱼ 和 dbⱼ。槽初始化、组映射和归约范围要保证每行贡献恰好计入一次。
+[T#B,!c47f17#边界]：即使令 G=M、每行独占一个槽，得到的仍是 \[M,N\] 行贡献，而非最终 \[N\] 梯度；仍需沿行/组维归约。这里描述 practice revision 2 的共享分组实现。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -136,15 +140,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LayerNorm 的 dx 为什么依赖整行上游梯度？</t>
+          <t xml:space="preserve">在 LayerNorm 反向中，一行输出的上游梯度为 dy，仿射缩放参数为 w。为什么某个输入分量的梯度 dxⱼ，不仅取决于本位置的 dyⱼ，还会受同一行其他位置的梯度影响？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：均值和方差由整行共享，所以每个输入分量都要扣除两项行内平均贡献。
-[E##dx=r\left(g-\operatorname{mean}(g)-\hat{x}\operatorname{mean}(g\hat{x})\right),\quad g=dy\cdot w]
-• [T#B#结果]：某位置的 dy 为0时，dx 仍可能因其他列改变行统计量而非零。
-[T#B,!c47f17#边界]：公式按同一归一化行求 mean；跨行不会进入该行的 dx。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为这一行的所有输入共同决定均值和方差；对任一输入求导时，除了该位置的直接路径，还必须计入它通过两项共享统计量影响整行输出的路径。
+• [T#B#符号定义]：令 g=dy×w 为逐元素加权上游梯度，r=1/sqrt(variance+epsilon) 为该行标准差倒数，x_hat=(x−mean)×r。下式所有 mean 都沿本行 N 个特征求平均。
+[E##dx_j=r\left(g_j-\operatorname{mean}(g)-\hat{x}_j\operatorname{mean}(g\hat{x})\right)]
+• [T#B#两项修正]：mean(g) 来自均值共享造成的修正；x_hatⱼ×mean(g×x_hat) 来自方差共享造成的修正。两项都汇总了整行，所以不同列的梯度发生耦合。
+[T#B,!c47f17#边界]：即使某个 dyⱼ=0，对应 dxⱼ 仍可能非零，因为两项行均值可能不为零。这里的耦合限于同一归一化行，其他行不会参与本行 dx 的计算。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,15 +166,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">常量行输出为 b，dx 必然为0吗？</t>
+          <t xml:space="preserve">LayerNorm 的一行输入全部等于同一个常数 a，归一化后 x_hat=0，因此前向输出等于偏置向量 b。能否由此断言这一行的输入梯度 dx 必为零？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不必然；函数在该点的输出值不能单独决定局部导数。
-• [T#B#反例]：若 x_hat=0、g=\[1+delta,1,1\]，则 dx=r\[2delta/3,-delta/3,-delta/3\]。
-• [T#B#不变量]：该反例仍满足行内 sum(dx)=0。
-[T#B,!c47f17#边界]：当加权上游梯度 g 在行内完全相同时，这个常量行的 dx 才退化为0。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。当前输入点的输出值为 b，只说明这一点的函数值；对输入做微小扰动时，均值和方差仍会变化，所以局部导数不一定为零。
+• [T#B#常量行的梯度式]：设 g=dy×w，r=1/sqrt(epsilon)，其中 dy 是上游梯度、w 是缩放参数、epsilon&gt;0。由于当前 x_hat=0，输入梯度简化为 dx=r×(g−mean(g))。
+• [T#B#具体反例]：取三列的加权上游梯度 g=\[1+delta,1,1\]，其中 delta≠0。其均值为 1+delta/3，因此 dx=r×\[2delta/3,−delta/3,−delta/3\]，显然不是全零。
+• [T#B#结果核对]：反例中三个 dx 分量的和仍为零，这与减去行平均的结构一致；“总和为零”也不能误读成“每个分量为零”。
+[T#B,!c47f17#边界]：在精确的常量行情形下，只有当 g 在行内各列相同时，上述中心化项才全部为零。有限精度实现还可能有额外舍入误差。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -186,15 +192,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAS 获取锁为何以返回0表示成功？</t>
+          <t xml:space="preserve">多个 Triton program 用同一标量锁保护共享梯度槽，约定锁值 0 表示空闲、1 表示占用。调用 tl.atomic_cas(lock,0,1) 时，为什么返回 0 才表示成功获得锁？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：atomic_cas 返回操作前的旧值；旧值为0时，它同时原子地把锁改为1。
-• [T#B#竞争者]：锁仍为1时，后续 CAS 返回1并继续自旋。
-• [T#B#为何原子]：若拆成 load 与 store，A、B 可先后都读到0，再都写1并进入临界区。
-[T#B,!c47f17#边界]：CAS 的原子性只裁决锁所有权，不单独保证受保护数据的跨 program 交接。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：atomic_cas 返回的是操作前的旧锁值。旧值等于比较值 0 时，它会在同一次原子操作中把锁改为 1；所以返回 0 表示自己完成了从空闲到占用的转换。
+• [T#B#未获得锁]：如果锁已经是 1，CAS 返回旧值 1，且不会把它改成自己拥有的空闲锁。竞争者需要继续等待或重试，不能进入临界区。
+• [T#B#为何不能拆开]：如果改为先 load 判断为 0、再 store 写 1，program A 和 B 可能都在写入前读到 0，然后都写 1 并认为自己成功，导致同时修改共享槽。
+[T#B,!c47f17#边界]：CAS 的不可分割性解决锁所有权竞争；受保护梯度数据如何从前一个 program 交给后一个，还需要匹配的同步和内存顺序语义。这里使用 Triton 3.7.1 的 CAS 语义。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -211,15 +217,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">relaxed CAS 成功为何不等于 buffer 已交接？</t>
+          <t xml:space="preserve">两个 Triton program 用同一标量锁轮流更新另一个地址上的梯度 buffer。后一个 program 的 relaxed CAS 已成功获得锁，为什么这还不足以保证它读到前一个 program 的完整 buffer 更新？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：relaxed 只保证锁位置的原子竞争，不为另一个 buffer 位置建立跨 program 的顺序与可见性。
-• [T#B#生产者]：release 把释放前、且已汇合到释放线程的更新纳入交接。
-• [T#B#消费者]：后续成功 acquire 接到该 release 后，再读取受保护数据。
-[T#B,!c47f17#边界]：acquire 需与匹配范围的 release 配合；它不会独自让所有内存变成“最新”。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为锁槽和梯度 buffer 是不同的内存位置。Relaxed 原子操作只保证锁槽上的竞争不可分割，不为周围的普通 buffer 读写建立所需的数据交接顺序与可见性。
+• [T#B#前一个 program]：生产者先完成受保护的向量更新，并让协作线程的写入汇合，再用 release 语义释放锁，把释放前的更新纳入同步交接。
+• [T#B#后一个 program]：消费者用 acquire 语义成功获取同一把锁；当该获取与对应 release 建立同步后，再读取 buffer，才能按这条同步链接收前面的受保护更新。
+• [T#B#两个保证]：CAS 原子性回答“谁获得锁”；release/acquire 回答“取得锁后如何接收前任留下的数据”。看见锁可用，不会自动让另一个地址上的数据满足相同保证。
+[T#B,!c47f17#边界]：Acquire 必须与合适范围内的 release 配合，不会单独把所有内存变成“最新”。同一 program 的协作线程还需先完成块内汇合，release 才能交接完整更新。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -236,16 +243,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 共享槽锁的三层保证是什么？</t>
+          <t xml:space="preserve">在 Triton LayerNorm 反向中，多个逐行 program 会轮流累加同一组梯度向量。CAS、解锁前的 block barrier、release/acquire 分别提供什么保证，为什么不能互相替代？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：三者依次解决锁所有权、program 内协作完成、program 间数据交接。
-• [T#B#CAS]：原子决定哪个 program 获得同一组的锁。
-• [T#B#barrier]：临界区向量写入后，让当前 block 的协作线程全部汇合。
-• [T#B#release/acquire]：把已汇合的更新交接给下一位成功获取同一锁的 program。
-[T#B,!c47f17#边界]：block barrier 不能替代跨 program 锁；CAS 原子性也不能替代数据可见性语义。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：三者分别保证“同一时刻谁能修改共享槽”“当前 program 的协作写入是否完成”“下一个 program 如何接收这些更新”，必须串成一条完整的锁协议。
+• [T#B#CAS：所有权]：对同一组锁原子地比较并修改，只让一个 program 成功进入临界区，避免两个 program 同时做读改写。
+• [T#B#Barrier：块内汇合]：共享梯度向量由当前 program 的多个线程协作处理。解锁前的 block barrier 让它们汇合，避免某个线程在其他分片尚未完成时提前释放锁。
+• [T#B#Release/acquire：交接]：当前持有者以 release 释放锁；下一位持有者以匹配的 acquire 成功获取锁后，再按同步链读取受保护的梯度数据。
+[T#B,!c47f17#边界]：Block barrier 只能协调当前 block，不能独自排斥其他 program；CAS 原子性只保护锁槽竞争，不能代替 buffer 的内存顺序与可见性保证。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -262,15 +269,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">官方 LayerNorm 反向不循环 N，为什么仍正确？</t>
+          <t xml:space="preserve">阅读固定版本 Triton 官方 LayerNorm 教程时，反向 kernel 只生成一次 tl.arange(0,BLOCK_SIZE_N)，没有沿行宽 N 循环。为什么它仍能覆盖整行，而不能据此判断漏算？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：wrapper 保证并复用 BLOCK_SIZE_N≥N，因此一次 tl.arange 已覆盖整行。
-• [T#B#前向循环]：在该 wrapper 接受的输入上，前向每段按 N 的循环实际也只迭代一次。
-• [T#B#阅读方法]：判断 kernel 是否漏算，必须同时检查 wrapper 的拒绝条件、launch 参数和保存的上下文。
-[T#B,!c47f17#边界]：绕过 wrapper 并令 BLOCK_SIZE_N&lt;N 时，反向会漏 dx，也会算错行内归约。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为教程的外层 wrapper 只接受能够由 BLOCK_SIZE_N 一次覆盖的行宽，并保证 BLOCK_SIZE_N≥N；反向复用这个值，因此一次索引生成已包含全部有效列。
+• [T#B#覆盖关系]：有效列为 0 到 N−1。生成 0 到 BLOCK_SIZE_N−1 后，只要 BLOCK_SIZE_N≥N，再用列号&lt;N 的 mask，就能完整处理有效列并排除 padding。
+• [T#B#为何前向看似不同]：同一 wrapper 的前提也约束前向，因此前向源码即使保留了沿 N 的分段循环，对它实际接受的输入也只执行一轮。源码存在循环不代表每次调用都会多轮执行。
+• [T#B#阅读方法]：判断是否漏算，要一起检查 wrapper 拒绝哪些输入、传入的 launch 参数，以及前向保存并在反向复用的上下文，不能只看 kernel 的循环形式。
+[T#B,!c47f17#边界]：这个结论绑定官方 tutorial 05 的 commit 35de6d6。若绕过 wrapper、强行令 BLOCK_SIZE_N&lt;N，单次索引就不再覆盖整行，dx 和行归约都会出错。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -287,15 +295,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dy*w 乘完再转 FP32，为什么太迟？</t>
+          <t xml:space="preserve">FP16 LayerNorm 反向计算加权上游梯度 g=dy×w 时，为什么应先把 dy 和 w 转为 FP32 再乘，而不是先做 FP16 乘法、再把乘积转为 FP32？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：FP16 乘积形成时差异已经可能被舍入掉，后续转换只能精确表示错误结果。
-• [T#B#修复位置]：先把 dy、w 转为 FP32，再形成 g=dy*w；归约循环和最终 dx 循环都要一致。
-• [T#B#反例]：精确乘积1.0004067和1可能都被FP16舍入成1，使本应非零的中心化梯度变成0。
-[T#B,!c47f17#边界]：FP32 累加器只能减小后续累加误差，不能恢复乘法阶段已丢失的信息。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为如果乘积已经在 FP16 中被舍入，两个本来不同的值可能变成相同结果；之后转为 FP32 只能保存这个已舍入结果，无法恢复被丢掉的差异。
+• [T#B#这些量用于哪里]：dy 是损失对输出的梯度，w 是仿射缩放参数；g 会参与 dx 中的行均值和中心化修正，因此相近乘积之间的微小差异也可能决定非零梯度。
+• [T#B#误差如何被放大]：例如精确乘积 1.0004067 和 1 都可能被 FP16 舍入成 1。后续即使用 FP32 计算 g−mean(g)，原本应存在的差异也已经消失，可能把非零的中心化结果算成 0。
+• [T#B#正确提升位置]：应先分别转换 dy、w，再执行 FP32 乘法。若实现分开循环计算行归约和最终 dx，两处都要采用相同的提升顺序，不能只修正其中一次乘法。
+[T#B,!c47f17#边界]：FP32 累加能减小后续累加误差，却不能修复低精度乘法已经造成的信息丢失；精度必须从需要保留差异的运算开始保证。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -312,15 +321,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">tl.div_rn 能修复哪些均值误差？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中计算 LayerNorm 均值 mean=sum(x)/N 时，把除法改为 tl.div_rn，能否消除均值误差及其对后续梯度的影响？</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它为当前 FP32 除法选择 round-to-nearest；不会回溯修复分子求和已有的舍入。
-• [T#B#误差放大]：若常量行保存 mean=a+eta，则每列 dw 行贡献为 -eta*r；同号误差可跨行累积。
-• [T#B#rstd]：同一偏差 mean 参与方差时得到 eta²，因此实际 r=1/sqrt(eta²+epsilon)。
-[T#B,!c47f17#边界]：精确舍入某一步不等于整条浮点归约精确，也不消除任意输入的求和误差。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能全部消除。Tl.div_rn 只对当前 FP32 除法执行 round-to-nearest 舍入；如果分子 sum(x) 早已带有求和误差，它不会回溯修复这部分误差。
+• [T#B#偏差场景]：考虑常量行 xⱼ=a，真实均值是 a，但保存的均值为 a+eta，其中 eta 是均值误差。为单独追踪这项偏差，以下先忽略后续计算的其他舍入误差。
+• [T#B#方差与 rstd]：每个中心化输入都是 −eta，沿行求平均平方得到方差 eta²。因此保存的标准差倒数为 r=1/sqrt(eta²+epsilon)，不能无条件替换成 1/sqrt(epsilon)。
+• [T#B#参数梯度后果]：若这行上游梯度 dyⱼ=1，则归一化输入为 −eta×r，每列对 dw 的贡献也为 −eta×r；一般 dyⱼ 下则为 −eta×r×dyⱼ。多行同号误差可能在参数梯度求和中累积。
+[T#B,!c47f17#边界]：精确舍入某一步，不等于整条浮点求和与归一化链条精确；这里既要检查均值分子的误差，也要使用实际保存的 rstd 分析后续影响。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -337,15 +347,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">两个反向 kernel 就表示参数梯度两阶段吗？</t>
+          <t xml:space="preserve">阅读某个框架的 LayerNorm 反向实现时，发现它启动了两个 kernel。能否据此断定 dw/db 必然先写入全局部分和缓冲区，再由第二个 kernel 归约？</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不表示；launch 数不能单独说明 dw/db 是否先物化部分和。
-• [T#B#工作划分]：dx 是行内归约，dw/db 是跨行归约；实现可分核直接算最终梯度，也可融合后写较少的 CTA 部分和。
-• [T#B#取舍]：省部分和可能增加输入重读；融合可复用数据，却带来缓冲区、同步和寄存器压力。
-[T#B,!c47f17#边界]：这是固定版本源码快照；同一框架也会按形状分派，kernel 更少不能直接推出更快。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。Kernel 启动次数只告诉你分了几次执行，不能说明每个 kernel 负责哪个梯度，也不能说明参数梯度是否先物化部分和。
+• [T#B#归约方向不同]：输入梯度 dx 依赖每行内部的归约；共享参数梯度 dw/db 则需要跨行求和。因此两个 kernel 可能分别负责 dx 和最终 dw/db，而不是同一个参数梯度的两个归约阶段。
+• [T#B#真正的两阶段]：另一类组织会让第一阶段写出参数梯度部分和，第二阶段再合并。部分和也不一定逐行保存为 \[M,N\]，可以按线程块（CTA）保存更少的部分和。
+• [T#B#如何看数据流]：应追踪每个 kernel 的输入、输出和临时 buffer：它写出的是最终梯度，还是待另一阶段消费的部分和。省去部分和可能增加输入重读；融合复用输入则可能增加同步、缓冲区和寄存器压力。
+[T#B,!c47f17#边界]：这里依据 PyTorch 2.13.0、Transformer Engine 1634a5a、Apex a1d527a 的固定源码比较。具体组织还会按形状和后端分派，kernel 更少不能直接推出更快。</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-05-layer-norm-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-05-layer-norm-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -50,7 +50,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">前导维→M，归一化维→N</t>
+          <t xml:space="preserve">前导维→M，归一化维→N；统计量 \[M\]，w/b \[N\] 跨行共享</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -68,10 +68,9 @@
       <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：因为填入的 0 在减去行均值后会变成 −mean；若继续平方并求和，无效位置就会额外贡献 mean²，污染本应只包含 N 个有效元素的方差。
-• [T#B#具体误差]：例如 N=5、计算块含 8 个位置、行均值为 2。三个无效位置若都参与平方，会多加 3×(−2)²=12，再除以 N=5，使方差额外增加 2.4。
+• [T#B#具体误差]：例如 N=5、计算块含 8 个位置、行均值为 2。三个无效位置若都参与平方，会多加 3×(−2)²=12，再除以 N=5，使方差额外增加 2.4；一般地，块长为 B 时多出 (B−N)×mean²/N。
 • [T#B#正确处理]：先以 FP32 计算有效元素的中心化值 x−mean，再把无效位置明确置为 0，最后平方、求和并除以有效长度 N。关键是不让 padding 对方差分子有任何贡献。
-• [T#B#为何不能只补 mean]：若 FP16 load 使用 other=mean，FP32 的 mean 可能先被舍入为 FP16；随后转回 FP32 并减原始 mean，padding 仍可能留下非零残差。
-[T#B,!c47f17#边界]：load mask 保证地址合法，并不自动保证后续变换的数学中性。方差归约中需要的是中心化后的无效贡献严格为零。</t>
+[T#B,!c47f17#边界]：load mask 保证地址合法，并不自动保证后续变换的数学中性。方差归约需要的是中心化后的无效贡献严格为零；改填其他值时同样要核对这一点。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -88,217 +87,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">在 Triton 3.7.1 中，逐行 LayerNorm 的输入是 FP16，前向用 tl.load(..., mask=cols&lt;N, other=mean) 给尾部 padding 填入 FP32 的行均值 mean，想让无效位置减均值后恰好为 0。为什么方差仍可能被污染？</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为 load 结果的类型是指针元素类型 FP16，other 会先被转成 FP16：FP32 的 mean 被舍入成 FP16 值。之后转回 FP32 再减原来的 mean，每个无效位置都留下残差（舍入后的 mean 减原 mean），平方后进入方差。
+• [T#B#残差有多大]：残差就是 mean 的 FP16 舍入误差，量级约为 mean 附近相邻 FP16 值的间距，而且每个无效位置都会出现一次。真实方差越小（例如近常量行），这点残差的相对影响越大。
+• [T#B#正确做法]：不依赖填充值：在 FP32 中先算中心化值 x−mean，再用 mask 把无效位置的中心化值置为 0，然后平方、求和、除以 N。
+[T#B,!c47f17#边界]：masked load 的 other 只决定无效位置读出什么值，不保证这个值在后续变换后仍然中性；换 dtype 或换填充值时都要重新核对。</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other 先转成 FP16 → 残差平方进方差</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · FP16 方差 padding</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">输入 X 为 \[M,N\]、每行独立归一化，前向为 Yᵢⱼ=x_hatᵢⱼ×wⱼ+bⱼ，其中 w、b 在所有行间共享。已知上游梯度 dY，参数梯度 dw、db 应如何计算、沿哪个轴归约？</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：对每个特征列 j，把所有 M 行对同一个共享参数的梯度贡献相加；最终 dw、db 的形状都为 \[N\]。
 • [T#B#符号定义]：dYᵢⱼ 是损失对输出 Yᵢⱼ 的梯度；x_hatᵢⱼ 是该行经过减均值、乘 rstd 后的归一化输入。i 遍历行，j 遍历特征列。
 [E##dw_j=\sum_{i=0}^{M-1}dY_{ij}\hat{x}_{ij},\qquad db_j=\sum_{i=0}^{M-1}dY_{ij}]
 • [T#B#局部与全局]：一个逐行 program 只能产生该行的长度 N 贡献向量；它不是最终参数梯度。需要继续沿行维求和，才能把所有使用同一 wⱼ、bⱼ 的贡献合并。
-[T#B,!c47f17#边界]：dw 乘的是归一化输入 x_hat，而不是原始 X；各行贡献带符号相加，可以互相抵消，例如 3 与 −5 的总和是 −2。</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+[T#B,!c47f17#边界]：dw 乘的是归一化输入 x_hat，而不是原始 X；各行贡献带符号相加，可以互相抵消。</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">dw 用 x_hat，db 用1，二者跨行求和</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 参数梯度</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在 LayerNorm 反向中，M 个逐行 program 要合并共享参数 w、b 的梯度。若 dw、db 分别使用 FP32 的 \[G,N\] 临时槽，怎样从这些槽得到最终 \[N\] 梯度？</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先把逐行贡献按 program 编号映射到 G 个组，在组锁保护下累加为组部分和；再启动第二个 kernel，沿 G 维归约这些部分和。
-• [T#B#各维含义]：M 是输入行数，N 是共享参数长度，G 是临时槽的组数。每个槽是一条长度 N 的向量，表示分配到该组的若干行的参数梯度贡献之和。
-• [T#B#第一阶段]：第 pid 行使用组号 pid%G。多个 program 若映射到同一组，就必须先获得该组的锁，再读取、更新并写回该组的 dw/db 槽，避免并发覆盖。
-• [T#B#第二阶段]：第一阶段结束后，对每个特征列 j，把组 0 到 G−1 的部分和相加，分别得到最终 dwⱼ 和 dbⱼ。槽初始化、组映射和归约范围要保证每行贡献恰好计入一次。
-[T#B,!c47f17#边界]：即使令 G=M、每行独占一个槽，得到的仍是 \[M,N\] 行贡献，而非最终 \[N\] 梯度；仍需沿行/组维归约。这里描述 practice revision 2 的共享分组实现。</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pid%G → 加锁累加 → 沿G归约</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lesson 05 · practice revision 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">在 LayerNorm 反向中，一行输出的上游梯度为 dy，仿射缩放参数为 w。为什么某个输入分量的梯度 dxⱼ，不仅取决于本位置的 dyⱼ，还会受同一行其他位置的梯度影响？</t>
+          <t xml:space="preserve">LayerNorm 反向中，M 个逐行 program 要合并共享参数 w、b 的梯度，但 dw、db 各只分配一份 FP32 的 \[G,N\] 临时槽（G&lt;M，多行共用一个槽）。第 pid 行的贡献写进哪个槽、同槽的多个 program 怎样避免互相覆盖、最后怎样得到 \[N\] 梯度？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：因为这一行的所有输入共同决定均值和方差；对任一输入求导时，除了该位置的直接路径，还必须计入它通过两项共享统计量影响整行输出的路径。
-• [T#B#符号定义]：令 g=dy×w 为逐元素加权上游梯度，r=1/sqrt(variance+epsilon) 为该行标准差倒数，x_hat=(x−mean)×r。下式所有 mean 都沿本行 N 个特征求平均。
-[E##dx_j=r\left(g_j-\operatorname{mean}(g)-\hat{x}_j\operatorname{mean}(g\hat{x})\right)]
-• [T#B#两项修正]：mean(g) 来自均值共享造成的修正；x_hatⱼ×mean(g×x_hat) 来自方差共享造成的修正。两项都汇总了整行，所以不同列的梯度发生耦合。
-[T#B,!c47f17#边界]：即使某个 dyⱼ=0，对应 dxⱼ 仍可能非零，因为两项行均值可能不为零。这里的耦合限于同一归一化行，其他行不会参与本行 dx 的计算。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：第 pid 行加到第 pid%G 组的槽：同组 program 先拿到该组的锁，再读旧部分和、加上本行贡献、写回；全部行累加完后，第二个 kernel 沿 G 维把各组部分和相加，得到最终 dw、db（各 \[N\]）。
+• [T#B#槽的含义]：每个槽是一条长度 N 的向量，保存分到该组的若干行贡献之和。例如 M=5、G=2 时，组 0 汇总 pid 0、2、4 的贡献，组 1 汇总 pid 1、3。
+• [T#B#为什么要锁]：累加是“读旧值→相加→写回”三步。两个同组 program 若同时读到旧值，各自写回后只会留下其中一个贡献，所以同组必须互斥地完成整段累加。
+• [T#B#第二阶段]：第一阶段结束后，对每列 j 把组 0 到 G−1 的部分和相加。槽初始化、组映射和归约范围要保证每行贡献恰好计入一次。
+[T#B,!c47f17#边界]：即使令 G=M、每行独占一个槽，得到的仍是 \[M,N\] 行贡献，仍需沿行（组）维归约；这里描述的是本课练习（practice revision 2）的共享分组实现。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">g、mean(g)、mean(g*x_hat)</t>
+          <t xml:space="preserve">pid%G → 加锁累加 → 沿G归约</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 输入梯度</t>
+          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 分组归约</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LayerNorm 的一行输入全部等于同一个常数 a，归一化后 x_hat=0，因此前向输出等于偏置向量 b。能否由此断言这一行的输入梯度 dx 必为零？</t>
+          <t xml:space="preserve">LayerNorm 反向要先暂存每行对 dw、db 的贡献，再归约成 \[N\]。比较两种暂存方案：每行独占一个槽（G=M，dw、db 各一份 FP32 \[M,N\]），与 G 组共享槽（各一份 \[G,N\]，G&lt;M）。两者各付出什么代价？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。当前输入点的输出值为 b，只说明这一点的函数值；对输入做微小扰动时，均值和方差仍会变化，所以局部导数不一定为零。
-• [T#B#常量行的梯度式]：设 g=dy×w，r=1/sqrt(epsilon)，其中 dy 是上游梯度、w 是缩放参数、epsilon&gt;0。由于当前 x_hat=0，输入梯度简化为 dx=r×(g−mean(g))。
-• [T#B#具体反例]：取三列的加权上游梯度 g=\[1+delta,1,1\]，其中 delta≠0。其均值为 1+delta/3，因此 dx=r×\[2delta/3,−delta/3,−delta/3\]，显然不是全零。
-• [T#B#结果核对]：反例中三个 dx 分量的和仍为零，这与减去行平均的结构一致；“总和为零”也不能误读成“每个分量为零”。
-[T#B,!c47f17#边界]：在精确的常量行情形下，只有当 g 在行内各列相同时，上述中心化项才全部为零。有限精度实现还可能有额外舍入误差。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：每行独占槽：各行写不同位置，没有读改写竞争、不需要锁，但两份 FP32 \[M,N\] 共占 8×M×N 字节；共享 G 组：空间降到两份 \[G,N\]，代价是同组 program 要争同一把锁、串行完成累加。
+• [T#B#空间]：例如 M=8192、N=4096 时，两份 FP32 \[M,N\] 部分和占 256 MiB；若只保存 128 行部分和，则为 4 MiB。
+• [T#B#竞争]：共享槽的累加是“读旧值→相加→写回”，必须在组锁保护下进行。每组分到约 M/G 行，G 越小，同一把锁上排队的 program 越多。
+[T#B,!c47f17#边界]：两种方案都还要第二阶段归约，G 只决定暂存粒度；8×M×N 只算参数梯度部分和，不是总 workspace。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">点值为b ≠ 雅可比为0</t>
+          <t xml:space="preserve">独占：无锁但 8MN 字节；共享 G：省空间但争锁</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 常量行反例</t>
+          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 分组取舍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">多个 Triton program 用同一标量锁保护共享梯度槽，约定锁值 0 表示空闲、1 表示占用。调用 tl.atomic_cas(lock,0,1) 时，为什么返回 0 才表示成功获得锁？</t>
+          <t xml:space="preserve">LayerNorm 反向中，一行的上游梯度为 dy、缩放参数为 w；令 g=dy×w，r 为该行的 rstd，x_hat=(x−mean)×r，mean(·) 表示沿本行 N 列求平均。dxⱼ 除了直接项 r×gⱼ，还有哪两项修正，各自来自哪个共享统计量？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：atomic_cas 返回的是操作前的旧锁值。旧值等于比较值 0 时，它会在同一次原子操作中把锁改为 1；所以返回 0 表示自己完成了从空闲到占用的转换。
-• [T#B#未获得锁]：如果锁已经是 1，CAS 返回旧值 1，且不会把它改成自己拥有的空闲锁。竞争者需要继续等待或重试，不能进入临界区。
-• [T#B#为何不能拆开]：如果改为先 load 判断为 0、再 store 写 1，program A 和 B 可能都在写入前读到 0，然后都写 1 并认为自己成功，导致同时修改共享槽。
-[T#B,!c47f17#边界]：CAS 的不可分割性解决锁所有权竞争；受保护梯度数据如何从前一个 program 交给后一个，还需要匹配的同步和内存顺序语义。这里使用 Triton 3.7.1 的 CAS 语义。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：两项修正是 −r×mean(g) 和 −r×x_hatⱼ×mean(g×x_hat)：前者来自整行共享的均值，后者来自整行共享的方差（经 rstd 传回）。合起来就是下式。
+[E##dx_j=r\left(g_j-\operatorname{mean}(g)-\hat{x}_j\operatorname{mean}(g\hat{x})\right)]
+• [T#B#为何耦合]：两个 mean 都汇总整行：改变任一输入都会改变本行的均值和方差，进而影响整行输出，所以 dxⱼ 也会收到同一行其他列 dy 的贡献。
+[T#B,!c47f17#边界]：即使某个 dyⱼ=0，对应 dxⱼ 仍可能非零；这种耦合只限同一归一化行，其他行不参与本行 dx 的计算。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">返回旧值；比较与修改不可分割</t>
+          <t xml:space="preserve">r×g − r×mean(g)（均值）− r×x_hat×mean(g×x_hat)（方差）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 05 · Triton 3.7.1 · CAS</t>
+          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 输入梯度</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">两个 Triton program 用同一标量锁轮流更新另一个地址上的梯度 buffer。后一个 program 的 relaxed CAS 已成功获得锁，为什么这还不足以保证它读到前一个 program 的完整 buffer 更新？</t>
+          <t xml:space="preserve">LayerNorm 反向中，固定 w、b、epsilon 和上游梯度 dy，并忽略浮点舍入。一行输入梯度的分量之和 Σⱼdxⱼ 等于多少？请从“整行输入都加上同一个常数 c 时输出怎样变化”来解释。</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：因为锁槽和梯度 buffer 是不同的内存位置。Relaxed 原子操作只保证锁槽上的竞争不可分割，不为周围的普通 buffer 读写建立所需的数据交接顺序与可见性。
-• [T#B#前一个 program]：生产者先完成受保护的向量更新，并让协作线程的写入汇合，再用 release 语义释放锁，把释放前的更新纳入同步交接。
-• [T#B#后一个 program]：消费者用 acquire 语义成功获取同一把锁；当该获取与对应 release 建立同步后，再读取 buffer，才能按这条同步链接收前面的受保护更新。
-• [T#B#两个保证]：CAS 原子性回答“谁获得锁”；release/acquire 回答“取得锁后如何接收前任留下的数据”。看见锁可用，不会自动让另一个地址上的数据满足相同保证。
-[T#B,!c47f17#边界]：Acquire 必须与合适范围内的 release 配合，不会单独把所有内存变成“最新”。同一 program 的协作线程还需先完成块内汇合，release 才能交接完整更新。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：Σⱼdxⱼ=0。整行加 c 时均值也加 c，中心化输入、方差、rstd 和 x_hat 都不变，所以输出 y 不变；而 Σⱼdxⱼ 正是损失沿“整行同加一个数”方向的变化率，输出不变，这个变化率就是 0。
+• [T#B#公式核对]：设 g=dy×w。由 dxⱼ=r×(gⱼ−mean(g)−x_hatⱼ×mean(g×x_hat)) 求和，得 r×(Σg−N×mean(g)−mean(g×x_hat)×Σx_hat)。前两项相消，而 Σx_hat=0，所以总和为 0。
+• [T#B#dx 也不变]：整行平移后 r 和 x_hat 不变，dy、w 又固定，所以这一行的 dx 本身也不变。
+[T#B,!c47f17#边界]：总和为 0 不表示每个分量为 0：常量行（x_hat=0、r=1/sqrt(epsilon)）的前向输出等于 b，但取 g=\[1+delta,1,1\] 时 dx=r×\[2delta/3,−delta/3,−delta/3\]；只有 g 在行内各列相同时 dx 才全为零。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">锁槽原子性 ≠ buffer 可见性</t>
+          <t xml:space="preserve">整行平移不改变 y → Σdx=0（Σx_hat=0）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 05 · 9/11 学习记录 · Triton/PTX</t>
+          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 平移不变与 Σdx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">在 Triton LayerNorm 反向中，多个逐行 program 会轮流累加同一组梯度向量。CAS、解锁前的 block barrier、release/acquire 分别提供什么保证，为什么不能互相替代？</t>
+          <t xml:space="preserve">两个 Triton program 用同一标量锁轮流更新另一个地址上的梯度 buffer，获锁与解锁都显式写成 sem="relaxed"。后一个 program 的 CAS 已成功拿到锁，为什么仍不能保证它读到前一个 program 写完的 buffer？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：三者分别保证“同一时刻谁能修改共享槽”“当前 program 的协作写入是否完成”“下一个 program 如何接收这些更新”，必须串成一条完整的锁协议。
-• [T#B#CAS：所有权]：对同一组锁原子地比较并修改，只让一个 program 成功进入临界区，避免两个 program 同时做读改写。
-• [T#B#Barrier：块内汇合]：共享梯度向量由当前 program 的多个线程协作处理。解锁前的 block barrier 让它们汇合，避免某个线程在其他分片尚未完成时提前释放锁。
-• [T#B#Release/acquire：交接]：当前持有者以 release 释放锁；下一位持有者以匹配的 acquire 成功获取锁后，再按同步链读取受保护的梯度数据。
-[T#B,!c47f17#边界]：Block barrier 只能协调当前 block，不能独自排斥其他 program；CAS 原子性只保护锁槽竞争，不能代替 buffer 的内存顺序与可见性保证。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为锁槽和梯度 buffer 是不同的内存位置。relaxed 原子操作只保证锁槽上的竞争不可分割，不为周围的普通 buffer 读写建立所需的数据交接顺序与可见性。
+• [T#B#前一个 program]：生产者先完成受保护的 buffer 更新，并让本 program 的协作线程汇合，再用 release 语义释放锁，把释放前的更新纳入交接。
+• [T#B#后一个 program]：消费者用 acquire 语义成功获取同一把锁，与对应的 release 建立同步后再读 buffer，才能看到前面的受保护更新。acquire 必须与合适范围内的 release 配对，不会单独把所有内存变成“最新”。
+• [T#B#两个保证]：CAS 原子性回答“谁拿到锁”；release/acquire 回答“拿到锁后能看到哪些数据”。看见锁可用，不会自动让另一个地址上的数据满足同样的保证。
+[T#B,!c47f17#边界]：在 Triton 3.7.1 中，tl.atomic_cas 与 tl.atomic_xchg 省略 sem、scope 时默认 acq_rel、gpu，所以教程不写 sem 的锁已经带有获锁 acquire、解锁 release；只有显式改成 relaxed 才会出现本题的问题。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有权 → 块内汇合 → 跨块交接</t>
+          <t xml:space="preserve">锁槽原子性 ≠ buffer 可见性</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 05 · 9/11 学习记录 · Triton 3.7.1</t>
+          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 锁与内存顺序</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">阅读固定版本 Triton 官方 LayerNorm 教程时，反向 kernel 只生成一次 tl.arange(0,BLOCK_SIZE_N)，没有沿行宽 N 循环。为什么它仍能覆盖整行，而不能据此判断漏算？</t>
+          <t xml:space="preserve">在 Triton LayerNorm 反向中，多个逐行 program 会轮流累加同一组梯度向量。CAS、解锁前的 block barrier、release/acquire 分别提供什么保证，为什么不能互相替代？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：三者分别保证“同一时刻谁能修改共享槽”“当前 program 的协作写入是否都已完成”“下一个 program 能否看到这些写入”，缺一项都不能构成完整的锁协议。
+• [T#B#CAS：所有权]：tl.atomic_cas(lock,0,1) 返回操作前的旧值：返回 0 表示本 program 完成了 0→1、拿到锁；返回 1 说明锁仍被占用，继续等待。比较与修改在一次原子操作中完成；若拆成先 load 判断、再 store 写 1，两个 program 可能都读到 0 而同时进入临界区。
+• [T#B#Barrier：块内汇合]：共享梯度向量由当前 program 的多个线程分片写入。解锁前的 block barrier 让它们汇合，避免执行解锁的线程在其他分片尚未写完时释放锁。
+• [T#B#Release/acquire：交接]：当前持有者以 release 解锁；下一位持有者以匹配的 acquire 成功获锁后，读到的槽才包含前任的全部更新。
+[T#B,!c47f17#边界]：block barrier 只协调当前 block，不能排斥其他 program，也不能代替跨 program 的 release/acquire。</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所有权 → 块内汇合 → 跨块交接</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 锁协议</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阅读官方 Triton LayerNorm 教程（tutorial 05，commit 35de6d6）时，反向 kernel 只生成一次 tl.arange(0,BLOCK_SIZE_N)，没有沿行宽 N 循环。为什么这不算漏算？</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：因为教程的外层 wrapper 只接受能够由 BLOCK_SIZE_N 一次覆盖的行宽，并保证 BLOCK_SIZE_N≥N；反向复用这个值，因此一次索引生成已包含全部有效列。
 • [T#B#覆盖关系]：有效列为 0 到 N−1。生成 0 到 BLOCK_SIZE_N−1 后，只要 BLOCK_SIZE_N≥N，再用列号&lt;N 的 mask，就能完整处理有效列并排除 padding。
 • [T#B#为何前向看似不同]：同一 wrapper 的前提也约束前向，因此前向源码即使保留了沿 N 的分段循环，对它实际接受的输入也只执行一轮。源码存在循环不代表每次调用都会多轮执行。
 • [T#B#阅读方法]：判断是否漏算，要一起检查 wrapper 拒绝哪些输入、传入的 launch 参数，以及前向保存并在反向复用的上下文，不能只看 kernel 的循环形式。
-[T#B,!c47f17#边界]：这个结论绑定官方 tutorial 05 的 commit 35de6d6。若绕过 wrapper、强行令 BLOCK_SIZE_N&lt;N，单次索引就不再覆盖整行，dx 和行归约都会出错。</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+[T#B,!c47f17#边界]：若绕过 wrapper、强行令 BLOCK_SIZE_N&lt;N，单次索引就不再覆盖整行，dx 和行内归约都会出错。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">wrapper 建立 N≤BLOCK_SIZE_N</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">Triton tutorial 05 · commit 35de6d6</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">FP16 LayerNorm 反向计算加权上游梯度 g=dy×w 时，为什么应先把 dy 和 w 转为 FP32 再乘，而不是先做 FP16 乘法、再把乘积转为 FP32？</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：因为如果乘积已经在 FP16 中被舍入，两个本来不同的值可能变成相同结果；之后转为 FP32 只能保存这个已舍入结果，无法恢复被丢掉的差异。
 • [T#B#这些量用于哪里]：dy 是损失对输出的梯度，w 是仿射缩放参数；g 会参与 dx 中的行均值和中心化修正，因此相近乘积之间的微小差异也可能决定非零梯度。
@@ -307,64 +329,90 @@
 [T#B,!c47f17#边界]：FP32 累加能减小后续累加误差，却不能修复低精度乘法已经造成的信息丢失；精度必须从需要保留差异的运算开始保证。</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">先提升操作数，再乘</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · FP16 dx 回归</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在 Triton 3.7.1 中计算 LayerNorm 均值 mean=sum(x)/N 时，把除法改为 tl.div_rn，能否消除均值误差及其对后续梯度的影响？</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能全部消除。Tl.div_rn 只对当前 FP32 除法执行 round-to-nearest 舍入；如果分子 sum(x) 早已带有求和误差，它不会回溯修复这部分误差。
-• [T#B#偏差场景]：考虑常量行 xⱼ=a，真实均值是 a，但保存的均值为 a+eta，其中 eta 是均值误差。为单独追踪这项偏差，以下先忽略后续计算的其他舍入误差。
-• [T#B#方差与 rstd]：每个中心化输入都是 −eta，沿行求平均平方得到方差 eta²。因此保存的标准差倒数为 r=1/sqrt(eta²+epsilon)，不能无条件替换成 1/sqrt(epsilon)。
-• [T#B#参数梯度后果]：若这行上游梯度 dyⱼ=1，则归一化输入为 −eta×r，每列对 dw 的贡献也为 −eta×r；一般 dyⱼ 下则为 −eta×r×dyⱼ。多行同号误差可能在参数梯度求和中累积。
-[T#B,!c47f17#边界]：精确舍入某一步，不等于整条浮点求和与归一化链条精确；这里既要检查均值分子的误差，也要使用实际保存的 rstd 分析后续影响。</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">只修当前除法，不修历史误差</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lesson 05 · Triton 3.7.1 · FP32 mean 回归</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">阅读某个框架的 LayerNorm 反向实现时，发现它启动了两个 kernel。能否据此断定 dw/db 必然先写入全局部分和缓冲区，再由第二个 kernel 归约？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 的 NVIDIA 后端上，LayerNorm 前向用普通除法 sum(x)/N 求 FP32 均值，FP32 常量行的 dw 回归超出容差；把这次除法改成 tl.div_rn 后回归通过。tl.div_rn 修的是哪一步误差，修不了什么？</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。Kernel 启动次数只告诉你分了几次执行，不能说明每个 kernel 负责哪个梯度，也不能说明参数梯度是否先物化部分和。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它修的是这一次除法的舍入：普通 / 在本课的 NVIDIA 编译产物里是近似除法 div.full.f32，tl.div_rn 改为 IEEE 最近舍入，回归因此通过；它修不了分子 sum(x) 此前已有的求和误差。
+• [T#B#根因]：常量行的正确 dw 为 0，实测最大偏差约 3.65e-4，超过 1e-4 容差。定位到均值的普通除法编译成了 div.full.f32；近似除法带来的微小均值偏差，经归一化和跨行累加后被放大到超差。
+• [T#B#写法]：把 N 转成 FP32，再用 tl.div_rn(sum, N_fp32) 求均值；它仍是 FP32 除法，只是舍入方式变成精确舍入。
+• [T#B#修不了什么]：tl.div_rn 只决定这一次除法怎样舍入；如果分子 sum(x) 已带有求和舍入误差，它不会回溯修正，链条上其他步骤的浮点误差也仍然存在。
+[T#B,!c47f17#边界]：div.full.f32 是在本课 NVIDIA 后端的编译产物里观察到的；换后端或换版本时，要重新查看实际生成的除法指令，不能直接套用。</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ 是近似除法 div.full.f32；div_rn 只修这一步</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · FP32 均值回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LayerNorm 前向中，有很多行都是常量行（行内所有 xⱼ=a），这些行保存的均值都带有同号的微小误差：mean=a+eta。设 epsilon=1e-5、所有 dyⱼ=1，保存的 rstd 记为 r。为什么这么小的 eta 也可能让最终 dw 超出测试容差？</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为这些常量行的方差几乎为 0，r 接近最大值 1/sqrt(epsilon)≈316，把 eta 放大成 x_hat=−eta×r；每行都给每个 dwⱼ 贡献 −eta×r，这些同号误差在跨行求和中不断累加。
+• [T#B#方差与 r]：用 a+eta 计算方差得 (1/N)×Σeta²=eta²，所以 r=1/sqrt(eta²+epsilon)；eta²≪epsilon 时 r≈1/sqrt(epsilon)。
+• [T#B#dw 贡献]：正确的 x_hat 应为 0，实际为 (a−(a+eta))×r=−eta×r；dyⱼ=1 时这一行对每个 dwⱼ 的贡献都是 −eta×r（一般为 −eta×r×dyⱼ），而正确贡献是 0。
+• [T#B#跨行累积]：dw 要沿 M 行求和，同号误差不会互相抵消，偏差随行数增长。本课 FP32 常量行回归中，正确 dw=0，实测最大偏差约 3.65e-4，超过 1e-4 容差。
+[T#B,!c47f17#边界]：一般式要用实际保存的 r=1/sqrt(eta²+epsilon)，不能直接写成 −eta/sqrt(epsilon)；后者只在 eta²≪epsilon 时近似成立。</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">方差≈0 → r≈1/√ε → x_hat=−eta×r → 同号累加</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 05 · 9/14 学习记录 · 均值误差传播</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阅读某个框架的 LayerNorm 反向实现时，发现它启动了两个 kernel。要判断 dw/db 是否先写入全局部分和缓冲区、再由第二个 kernel 归约，应该看什么，为什么只看 kernel 数不够？</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：要看数据流：追踪每个 kernel 读写哪些 buffer，它写出的是最终 dw/db，还是供另一阶段消费的部分和。kernel 数只说明分了几次执行，不说明每个 kernel 负责哪个梯度。
 • [T#B#归约方向不同]：输入梯度 dx 依赖每行内部的归约；共享参数梯度 dw/db 则需要跨行求和。因此两个 kernel 可能分别负责 dx 和最终 dw/db，而不是同一个参数梯度的两个归约阶段。
 • [T#B#真正的两阶段]：另一类组织会让第一阶段写出参数梯度部分和，第二阶段再合并。部分和也不一定逐行保存为 \[M,N\]，可以按线程块（CTA）保存更少的部分和。
-• [T#B#如何看数据流]：应追踪每个 kernel 的输入、输出和临时 buffer：它写出的是最终梯度，还是待另一阶段消费的部分和。省去部分和可能增加输入重读；融合复用输入则可能增加同步、缓冲区和寄存器压力。
+• [T#B#代价取舍]：省去部分和可能要分别重读输入；融合复用输入则可能增加同步、缓冲区和寄存器压力。
 [T#B,!c47f17#边界]：这里依据 PyTorch 2.13.0、Transformer Engine 1634a5a、Apex a1d527a 的固定源码比较。具体组织还会按形状和后端分派，kernel 更少不能直接推出更快。</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">kernel 数 ≠ 参数梯度归约阶段数</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">Lesson 05 · 9/10 固定源码比较</t>
         </is>
